--- a/modules/segment/docs/templates/Segment_Config_Template.xlsx
+++ b/modules/segment/docs/templates/Segment_Config_Template.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
   <si>
     <t xml:space="preserve">Setting</t>
   </si>
@@ -697,7 +697,13 @@
     <t xml:space="preserve">research_house</t>
   </si>
   <si>
-    <t xml:space="preserve">Research organisation name for stats pack Declaration sheet</t>
+    <t xml:space="preserve">Research organisation name. Appears on the report header and footer and on the stats pack Declaration sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client the report was prepared for. Appears on the report header and footer.</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -2575,6 +2581,23 @@
         <v>132</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s">
+        <v>221</v>
+      </c>
+      <c r="E78" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -2766,50 +2789,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2829,74 +2852,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -2925,7 +2948,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
         <v>208</v>
@@ -2933,55 +2956,55 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -3005,32 +3028,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>

--- a/modules/segment/docs/templates/Segment_Config_Template.xlsx
+++ b/modules/segment/docs/templates/Segment_Config_Template.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
   <si>
     <t xml:space="preserve">Setting</t>
   </si>
@@ -706,6 +706,21 @@
     <t xml:space="preserve">Client the report was prepared for. Appears on the report header and footer.</t>
   </si>
   <si>
+    <t xml:space="preserve">tabs_export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write the segment column back onto the survey file, plus a banner stub for tabs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allow_partial_join</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allow the tabs export when some survey rows have no segment. They become 'Unassigned'.</t>
+  </si>
+  <si>
     <t xml:space="preserve">variable</t>
   </si>
   <si>
@@ -826,7 +841,7 @@
     <t xml:space="preserve">date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-20</t>
+    <t xml:space="preserve">2026-09-21</t>
   </si>
   <si>
     <t xml:space="preserve">confidentiality</t>
@@ -2598,12 +2613,46 @@
         <v>132</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>225</v>
+      </c>
+      <c r="B80" t="s">
+        <v>223</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" t="s">
+        <v>226</v>
+      </c>
+      <c r="E80" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="28">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="30">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"kmeans,hclust,gmm,all"</xm:f>
@@ -2645,6 +2694,18 @@
             <xm:f>"descriptive,persona,simple"</xm:f>
           </x14:formula1>
           <xm:sqref>B45:B45</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B79:B79</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B80:B80</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -2789,50 +2850,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2852,74 +2913,74 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B8" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2948,7 +3009,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B2" t="s">
         <v>208</v>
@@ -2956,55 +3017,55 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -3028,32 +3089,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
